--- a/data/pendaftaran_anggota.xlsx
+++ b/data/pendaftaran_anggota.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -426,11 +426,12 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,25 +467,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>simpanan_pokok</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tanggal_pengajuan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>catatan_admin</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_anggota_dibuat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>no_anggota_dibuat</t>
         </is>

--- a/data/pendaftaran_anggota.xlsx
+++ b/data/pendaftaran_anggota.xlsx
@@ -417,21 +417,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,55 +444,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>nama</t>
+          <t>nama_lengkap</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>no_hp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>alamat</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>no_telp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>kategori_anggota</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>penghasilan_bersih</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cicilan_lain</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>simpanan_pokok</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tanggal_pengajuan</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>catatan_admin</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>id_anggota_dibuat</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>no_anggota_dibuat</t>
         </is>
